--- a/Survey_Responses.xlsx
+++ b/Survey_Responses.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/home/Desktop/AIModelQuality/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9AB81C6E-0BF0-9445-A8FC-63B884720195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9565C92D-E86D-344B-A39D-E180A03C4A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4580" yWindow="-21000" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-37680" yWindow="3440" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="第 1 张表单回复" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="473">
   <si>
     <t>第 1 列</t>
   </si>
@@ -1457,6 +1456,10 @@
   </si>
   <si>
     <t>[Perception 7] Beyond meeting compliance requirements, prioritizing explainability serves a dual purpose: it helps AI developers debug their models and builds human-AI trust by providing the rationale behind decisions. While industry practitioners used to</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Average</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1468,7 +1471,7 @@
     <numFmt numFmtId="176" formatCode="yyyy\-m\-d\ am/pmhh:mm:ss"/>
     <numFmt numFmtId="177" formatCode="m/d/yyyy\ h:mm:ss"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1496,6 +1499,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1517,7 +1528,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1533,6 +1544,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2110,7 +2124,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
+        <b/>
         <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
@@ -2119,10 +2133,9 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
+        <sz val="16"/>
         <color theme="1"/>
         <name val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2214,30 +2227,6 @@
       </fill>
     </dxf>
     <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF5B3F86"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF5B3F86"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF5B3F86"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF5B3F86"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD6CFE0"/>
-          <bgColor rgb="FFD6CFE0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFF8F9FA"/>
@@ -2256,19 +2245,43 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFD6CFE0"/>
+          <bgColor rgb="FFD6CFE0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FF5B3F86"/>
           <bgColor rgb="FF5B3F86"/>
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF5B3F86"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF5B3F86"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF5B3F86"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF5B3F86"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="2">
     <tableStyle name="第 1 张表单回复-style" pivot="0" count="5" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="37"/>
-      <tableStyleElement type="headerRow" dxfId="41"/>
-      <tableStyleElement type="totalRow" dxfId="38"/>
-      <tableStyleElement type="firstRowStripe" dxfId="40"/>
-      <tableStyleElement type="secondRowStripe" dxfId="39"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="41"/>
+      <tableStyleElement type="headerRow" dxfId="40"/>
+      <tableStyleElement type="totalRow" dxfId="39"/>
+      <tableStyleElement type="firstRowStripe" dxfId="38"/>
+      <tableStyleElement type="secondRowStripe" dxfId="37"/>
     </tableStyle>
     <tableStyle name="第 1 张表单回复-style 2" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
       <tableStyleElement type="firstRowStripe" dxfId="36"/>
@@ -2292,7 +2305,7 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="第 1 列" totalsRowDxfId="33"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="第 2 列" totalsRowDxfId="32"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="第 3 列" totalsRowDxfId="31"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="What specific areas of expertise have you applied in the industry? (e.g., recommendation systems)" totalsRowDxfId="30"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="What specific areas of expertise have you applied in the industry? (e.g., recommendation systems)" totalsRowLabel="Average" totalsRowDxfId="30"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="What is your role? (e.g., ML Engineer, AI Scientist)" totalsRowDxfId="29"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="How many years of industry experience do you have in AI development?" totalsRowFunction="custom" totalsRowDxfId="28">
       <totalsRowFormula>MEDIAN(Form_Responses[How many years of industry experience do you have in AI development?])</totalsRowFormula>
@@ -2308,7 +2321,7 @@
     </tableColumn>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Comments for the above question:" totalsRowDxfId="24"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="[Perception 2] While previously considered challenging, deployability and scalability are now handled by microservices. AI teams containerize models and expose APIs for easy deployment and intergration, and rely on platform infrastructure (e,g, cloud serv" totalsRowFunction="custom" totalsRowDxfId="23">
-      <totalsRowFormula>AVERAGE(#REF!)</totalsRowFormula>
+      <totalsRowFormula>AVERAGE(Form_Responses['[Perception 2'] While previously considered challenging, deployability and scalability are now handled by microservices. AI teams containerize models and expose APIs for easy deployment and intergration, and rely on platform infrastructure (e,g, cloud serv])</totalsRowFormula>
     </tableColumn>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Comments for the above question: 2" totalsRowDxfId="22"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="[Perception 3] Safety regulations necessitate robustness as a primary quality attribute for generative AI applications to  ensure that outputs are non-discriminatory, safe, and legally compliant." totalsRowFunction="custom" totalsRowDxfId="21">
@@ -2328,7 +2341,7 @@
     </tableColumn>
     <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Comments for the above question: 6" totalsRowDxfId="14"/>
     <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="[Perception 7] Beyond meeting compliance requirements, prioritizing explainability serves a dual purpose: it helps AI developers debug their models and builds human-AI trust by providing the rationale behind decisions. While industry practitioners used to" totalsRowFunction="custom" totalsRowDxfId="13">
-      <totalsRowFormula>AVERAGE(#REF!)</totalsRowFormula>
+      <totalsRowFormula>AVERAGE(Form_Responses['[Perception 7'] Beyond meeting compliance requirements, prioritizing explainability serves a dual purpose: it helps AI developers debug their models and builds human-AI trust by providing the rationale behind decisions. While industry practitioners used to])</totalsRowFormula>
     </tableColumn>
     <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Comments for the above question: 7" totalsRowDxfId="12"/>
     <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="[Perception 8] AI model brings new robustness requirements. In volatile domains (e.g., security, fraud), robustness is prioritized to fight against class imbalance and data drift." totalsRowFunction="custom" totalsRowDxfId="11">
@@ -2609,7 +2622,7 @@
     <col min="35" max="40" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" s="6" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:34" s="6" customFormat="1" ht="97" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -6901,7 +6914,9 @@
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
+      <c r="D52" s="7" t="s">
+        <v>472</v>
+      </c>
       <c r="E52" s="2"/>
       <c r="F52" s="2">
         <f>MEDIAN(Form_Responses[How many years of industry experience do you have in AI development?])</f>
@@ -6920,9 +6935,9 @@
         <v>4.16</v>
       </c>
       <c r="J52" s="2"/>
-      <c r="K52" s="2" t="e">
-        <f>AVERAGE(#REF!)</f>
-        <v>#REF!</v>
+      <c r="K52" s="2">
+        <f>AVERAGE(Form_Responses['[Perception 2'] While previously considered challenging, deployability and scalability are now handled by microservices. AI teams containerize models and expose APIs for easy deployment and intergration, and rely on platform infrastructure (e,g, cloud serv])</f>
+        <v>4.0204081632653059</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" s="2">
@@ -6945,9 +6960,9 @@
         <v>4.38</v>
       </c>
       <c r="T52" s="2"/>
-      <c r="U52" s="2" t="e">
-        <f>AVERAGE(#REF!)</f>
-        <v>#REF!</v>
+      <c r="U52" s="2">
+        <f>AVERAGE(Form_Responses['[Perception 7'] Beyond meeting compliance requirements, prioritizing explainability serves a dual purpose: it helps AI developers debug their models and builds human-AI trust by providing the rationale behind decisions. While industry practitioners used to])</f>
+        <v>4.1836734693877551</v>
       </c>
       <c r="V52" s="2"/>
       <c r="W52" s="2">
